--- a/COSTO_FIJO_ACTUALIZADO.xlsx
+++ b/COSTO_FIJO_ACTUALIZADO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8a3802af127234b/Documentos/GitHub/sicetac-api/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{14F614BD-C898-43BC-9636-3F9A2D0EF330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54253E91-119F-4D4B-ABC5-813B3EF338D2}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{14F614BD-C898-43BC-9636-3F9A2D0EF330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4B77718-2CC8-4CF3-94C4-64D338E4A100}"/>
   <bookViews>
-    <workbookView xWindow="1335" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FE6DA646-F4A1-41C8-9D6F-96FD91E2052D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{FE6DA646-F4A1-41C8-9D6F-96FD91E2052D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -553,7 +553,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -581,7 +581,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -595,7 +595,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -637,7 +637,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
@@ -679,7 +679,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -693,7 +693,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -707,7 +707,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -749,7 +749,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -791,7 +791,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -833,7 +833,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -847,7 +847,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -875,7 +875,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
@@ -917,7 +917,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B28" t="s">
         <v>3</v>
@@ -931,7 +931,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
@@ -973,7 +973,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
@@ -1015,7 +1015,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
@@ -1043,7 +1043,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
@@ -1057,7 +1057,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B38" t="s">
         <v>4</v>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B42" t="s">
         <v>5</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B43" t="s">
         <v>5</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B44" t="s">
         <v>5</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B45" t="s">
         <v>5</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B47" t="s">
         <v>5</v>
@@ -1197,7 +1197,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B48" t="s">
         <v>5</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B49" t="s">
         <v>5</v>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B50" t="s">
         <v>5</v>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B51" t="s">
         <v>5</v>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B52" t="s">
         <v>5</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B53" t="s">
         <v>6</v>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B54" t="s">
         <v>6</v>
@@ -1295,7 +1295,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B55" t="s">
         <v>6</v>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B56" t="s">
         <v>6</v>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B57" t="s">
         <v>6</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B58" t="s">
         <v>6</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B59" t="s">
         <v>6</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B60" t="s">
         <v>6</v>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B61" t="s">
         <v>6</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B62" t="s">
         <v>6</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B63" t="s">
         <v>6</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B64" t="s">
         <v>6</v>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B65" t="s">
         <v>7</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B66" t="s">
         <v>7</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B67" t="s">
         <v>7</v>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B68" t="s">
         <v>7</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B69" t="s">
         <v>7</v>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B70" t="s">
         <v>7</v>
@@ -1519,7 +1519,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B71" t="s">
         <v>7</v>
@@ -1533,7 +1533,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B72" t="s">
         <v>7</v>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B73" t="s">
         <v>7</v>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B74" t="s">
         <v>7</v>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B75" t="s">
         <v>7</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B76" t="s">
         <v>7</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B77" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B78" t="s">
         <v>8</v>
@@ -1631,7 +1631,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B79" t="s">
         <v>8</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B80" t="s">
         <v>8</v>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B81" t="s">
         <v>8</v>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B82" t="s">
         <v>8</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B83" t="s">
         <v>8</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B84" t="s">
         <v>8</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B85" t="s">
         <v>8</v>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B86" t="s">
         <v>8</v>
@@ -1743,7 +1743,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B87" t="s">
         <v>8</v>
@@ -1757,7 +1757,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B88" t="s">
         <v>8</v>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B89" t="s">
         <v>9</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B90" t="s">
         <v>9</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B91" t="s">
         <v>9</v>
@@ -1813,7 +1813,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B92" t="s">
         <v>9</v>
@@ -1827,7 +1827,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B93" t="s">
         <v>9</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B94" t="s">
         <v>9</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B95" t="s">
         <v>9</v>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B96" t="s">
         <v>9</v>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B97" t="s">
         <v>9</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B98" t="s">
         <v>9</v>
@@ -1911,7 +1911,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B99" t="s">
         <v>9</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B100" t="s">
         <v>9</v>

--- a/COSTO_FIJO_ACTUALIZADO.xlsx
+++ b/COSTO_FIJO_ACTUALIZADO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8a3802af127234b/Documentos/GitHub/sicetac-api/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{14F614BD-C898-43BC-9636-3F9A2D0EF330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4B77718-2CC8-4CF3-94C4-64D338E4A100}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{14F614BD-C898-43BC-9636-3F9A2D0EF330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EF6E27D-5D06-4A99-871F-C951C6A5042C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{FE6DA646-F4A1-41C8-9D6F-96FD91E2052D}"/>
   </bookViews>
@@ -553,7 +553,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -581,7 +581,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -595,7 +595,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -637,7 +637,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
@@ -679,7 +679,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -693,7 +693,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -707,7 +707,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -749,7 +749,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -791,7 +791,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -833,7 +833,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -847,7 +847,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -875,7 +875,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
@@ -917,7 +917,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B28" t="s">
         <v>3</v>
@@ -931,7 +931,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
@@ -973,7 +973,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
@@ -987,7 +987,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
@@ -1015,7 +1015,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
@@ -1043,7 +1043,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
@@ -1057,7 +1057,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B38" t="s">
         <v>4</v>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B42" t="s">
         <v>5</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B43" t="s">
         <v>5</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B44" t="s">
         <v>5</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B45" t="s">
         <v>5</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B47" t="s">
         <v>5</v>
@@ -1197,7 +1197,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B48" t="s">
         <v>5</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B49" t="s">
         <v>5</v>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B50" t="s">
         <v>5</v>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B51" t="s">
         <v>5</v>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B52" t="s">
         <v>5</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B53" t="s">
         <v>6</v>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B54" t="s">
         <v>6</v>
@@ -1295,7 +1295,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B55" t="s">
         <v>6</v>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B56" t="s">
         <v>6</v>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B57" t="s">
         <v>6</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B58" t="s">
         <v>6</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B59" t="s">
         <v>6</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B60" t="s">
         <v>6</v>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B61" t="s">
         <v>6</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B62" t="s">
         <v>6</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B63" t="s">
         <v>6</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B64" t="s">
         <v>6</v>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B65" t="s">
         <v>7</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B66" t="s">
         <v>7</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B67" t="s">
         <v>7</v>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B68" t="s">
         <v>7</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B69" t="s">
         <v>7</v>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B70" t="s">
         <v>7</v>
@@ -1519,7 +1519,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B71" t="s">
         <v>7</v>
@@ -1533,7 +1533,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B72" t="s">
         <v>7</v>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B73" t="s">
         <v>7</v>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B74" t="s">
         <v>7</v>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B75" t="s">
         <v>7</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B76" t="s">
         <v>7</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B77" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B78" t="s">
         <v>8</v>
@@ -1631,7 +1631,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B79" t="s">
         <v>8</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B80" t="s">
         <v>8</v>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B81" t="s">
         <v>8</v>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B82" t="s">
         <v>8</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B83" t="s">
         <v>8</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B84" t="s">
         <v>8</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B85" t="s">
         <v>8</v>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B86" t="s">
         <v>8</v>
@@ -1743,7 +1743,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B87" t="s">
         <v>8</v>
@@ -1757,7 +1757,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B88" t="s">
         <v>8</v>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B89" t="s">
         <v>9</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B90" t="s">
         <v>9</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B91" t="s">
         <v>9</v>
@@ -1813,7 +1813,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B92" t="s">
         <v>9</v>
@@ -1827,7 +1827,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B93" t="s">
         <v>9</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B94" t="s">
         <v>9</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B95" t="s">
         <v>9</v>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B96" t="s">
         <v>9</v>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B97" t="s">
         <v>9</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B98" t="s">
         <v>9</v>
@@ -1911,7 +1911,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B99" t="s">
         <v>9</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B100" t="s">
         <v>9</v>

--- a/COSTO_FIJO_ACTUALIZADO.xlsx
+++ b/COSTO_FIJO_ACTUALIZADO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8a3802af127234b/Documentos/GitHub/sicetac-api/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{14F614BD-C898-43BC-9636-3F9A2D0EF330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EF6E27D-5D06-4A99-871F-C951C6A5042C}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{14F614BD-C898-43BC-9636-3F9A2D0EF330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152887BD-2589-4455-BC4B-E4365DE69185}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{FE6DA646-F4A1-41C8-9D6F-96FD91E2052D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="25">
   <si>
     <t>TIPO_VEHICULO</t>
   </si>
@@ -185,13 +185,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -527,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D7E9A6-EF64-4041-8EB1-689E9E14726C}">
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
@@ -1937,6 +1938,1392 @@
         <v>13698206.59</v>
       </c>
     </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>202602</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1</v>
+      </c>
+      <c r="C101" t="s">
+        <v>12</v>
+      </c>
+      <c r="D101" s="4">
+        <v>8722476.4900000002</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>202602</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" s="4">
+        <v>8722476.4900000002</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>202602</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1</v>
+      </c>
+      <c r="C103" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" s="4">
+        <v>8722476.4900000002</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>202602</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" t="s">
+        <v>15</v>
+      </c>
+      <c r="D104" s="4">
+        <v>8946923.4900000002</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>202602</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1</v>
+      </c>
+      <c r="C105" t="s">
+        <v>23</v>
+      </c>
+      <c r="D105" s="4">
+        <v>8946923.4900000002</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>202602</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
+        <v>16</v>
+      </c>
+      <c r="D106" s="4">
+        <v>8946923.4900000002</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>202602</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1</v>
+      </c>
+      <c r="C107" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" s="4">
+        <v>12926897.49</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>202602</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108" t="s">
+        <v>18</v>
+      </c>
+      <c r="D108" s="4">
+        <v>9563859.4900000002</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>202602</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1</v>
+      </c>
+      <c r="C109" t="s">
+        <v>19</v>
+      </c>
+      <c r="D109" s="4">
+        <v>13523345.49</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>202602</v>
+      </c>
+      <c r="B110" t="s">
+        <v>2</v>
+      </c>
+      <c r="C110" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" s="4">
+        <v>8899981.4900000002</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>202602</v>
+      </c>
+      <c r="B111" t="s">
+        <v>2</v>
+      </c>
+      <c r="C111" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" s="4">
+        <v>8899981.4900000002</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>202602</v>
+      </c>
+      <c r="B112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C112" t="s">
+        <v>14</v>
+      </c>
+      <c r="D112" s="4">
+        <v>8899981.4900000002</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>202602</v>
+      </c>
+      <c r="B113" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" t="s">
+        <v>15</v>
+      </c>
+      <c r="D113" s="4">
+        <v>9124428.4900000002</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>202602</v>
+      </c>
+      <c r="B114" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114" t="s">
+        <v>23</v>
+      </c>
+      <c r="D114" s="4">
+        <v>9124428.4900000002</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>202602</v>
+      </c>
+      <c r="B115" t="s">
+        <v>2</v>
+      </c>
+      <c r="C115" t="s">
+        <v>16</v>
+      </c>
+      <c r="D115" s="4">
+        <v>9124428.4900000002</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>202602</v>
+      </c>
+      <c r="B116" t="s">
+        <v>2</v>
+      </c>
+      <c r="C116" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" s="4">
+        <v>9327259.4900000002</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>202602</v>
+      </c>
+      <c r="B117" t="s">
+        <v>2</v>
+      </c>
+      <c r="C117" t="s">
+        <v>18</v>
+      </c>
+      <c r="D117" s="4">
+        <v>9551706.4900000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>202602</v>
+      </c>
+      <c r="B118" t="s">
+        <v>2</v>
+      </c>
+      <c r="C118" t="s">
+        <v>19</v>
+      </c>
+      <c r="D118" s="4">
+        <v>13616195.49</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>202602</v>
+      </c>
+      <c r="B119" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" s="4">
+        <v>9507606.4900000002</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>202602</v>
+      </c>
+      <c r="B120" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="4">
+        <v>9507606.4900000002</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>202602</v>
+      </c>
+      <c r="B121" t="s">
+        <v>3</v>
+      </c>
+      <c r="C121" t="s">
+        <v>14</v>
+      </c>
+      <c r="D121" s="4">
+        <v>9507606.4900000002</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>202602</v>
+      </c>
+      <c r="B122" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="4">
+        <v>9732053.4900000002</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>202602</v>
+      </c>
+      <c r="B123" t="s">
+        <v>3</v>
+      </c>
+      <c r="C123" t="s">
+        <v>23</v>
+      </c>
+      <c r="D123" s="4">
+        <v>9732053.4900000002</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>202602</v>
+      </c>
+      <c r="B124" t="s">
+        <v>3</v>
+      </c>
+      <c r="C124" t="s">
+        <v>16</v>
+      </c>
+      <c r="D124" s="4">
+        <v>9732053.4900000002</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>202602</v>
+      </c>
+      <c r="B125" t="s">
+        <v>3</v>
+      </c>
+      <c r="C125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" s="4">
+        <v>10082096.49</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>202602</v>
+      </c>
+      <c r="B126" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" t="s">
+        <v>18</v>
+      </c>
+      <c r="D126" s="4">
+        <v>10306543.49</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>202602</v>
+      </c>
+      <c r="B127" t="s">
+        <v>3</v>
+      </c>
+      <c r="C127" t="s">
+        <v>19</v>
+      </c>
+      <c r="D127" s="4">
+        <v>14377192.49</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>202602</v>
+      </c>
+      <c r="B128" t="s">
+        <v>4</v>
+      </c>
+      <c r="C128" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" s="4">
+        <v>11760277.49</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>202602</v>
+      </c>
+      <c r="B129" t="s">
+        <v>4</v>
+      </c>
+      <c r="C129" t="s">
+        <v>13</v>
+      </c>
+      <c r="D129" s="4">
+        <v>11760277.49</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>202602</v>
+      </c>
+      <c r="B130" t="s">
+        <v>4</v>
+      </c>
+      <c r="C130" t="s">
+        <v>14</v>
+      </c>
+      <c r="D130" s="4">
+        <v>11760277.49</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>202602</v>
+      </c>
+      <c r="B131" t="s">
+        <v>4</v>
+      </c>
+      <c r="C131" t="s">
+        <v>15</v>
+      </c>
+      <c r="D131" s="4">
+        <v>11984724.49</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>202602</v>
+      </c>
+      <c r="B132" t="s">
+        <v>4</v>
+      </c>
+      <c r="C132" t="s">
+        <v>23</v>
+      </c>
+      <c r="D132" s="4">
+        <v>11984724.49</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>202602</v>
+      </c>
+      <c r="B133" t="s">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>16</v>
+      </c>
+      <c r="D133" s="4">
+        <v>11984724.49</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>202602</v>
+      </c>
+      <c r="B134" t="s">
+        <v>4</v>
+      </c>
+      <c r="C134" t="s">
+        <v>17</v>
+      </c>
+      <c r="D134" s="4">
+        <v>12926897.49</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>202602</v>
+      </c>
+      <c r="B135" t="s">
+        <v>4</v>
+      </c>
+      <c r="C135" t="s">
+        <v>18</v>
+      </c>
+      <c r="D135" s="4">
+        <v>13151344.49</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>202602</v>
+      </c>
+      <c r="B136" t="s">
+        <v>4</v>
+      </c>
+      <c r="C136" t="s">
+        <v>19</v>
+      </c>
+      <c r="D136" s="4">
+        <v>16483739.49</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>202602</v>
+      </c>
+      <c r="B137" t="s">
+        <v>4</v>
+      </c>
+      <c r="C137" t="s">
+        <v>20</v>
+      </c>
+      <c r="D137" s="4">
+        <v>11760277.49</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>202602</v>
+      </c>
+      <c r="B138" t="s">
+        <v>4</v>
+      </c>
+      <c r="C138" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138" s="4">
+        <v>13056463.49</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>202602</v>
+      </c>
+      <c r="B139" t="s">
+        <v>4</v>
+      </c>
+      <c r="C139" t="s">
+        <v>24</v>
+      </c>
+      <c r="D139" s="4">
+        <v>12364027.49</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>202602</v>
+      </c>
+      <c r="B140" t="s">
+        <v>5</v>
+      </c>
+      <c r="C140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D140" s="4">
+        <v>12529494.49</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>202602</v>
+      </c>
+      <c r="B141" t="s">
+        <v>5</v>
+      </c>
+      <c r="C141" t="s">
+        <v>13</v>
+      </c>
+      <c r="D141" s="4">
+        <v>12529494.49</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>202602</v>
+      </c>
+      <c r="B142" t="s">
+        <v>5</v>
+      </c>
+      <c r="C142" t="s">
+        <v>14</v>
+      </c>
+      <c r="D142" s="4">
+        <v>12529494.49</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>202602</v>
+      </c>
+      <c r="B143" t="s">
+        <v>5</v>
+      </c>
+      <c r="C143" t="s">
+        <v>15</v>
+      </c>
+      <c r="D143" s="4">
+        <v>12753941.49</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>202602</v>
+      </c>
+      <c r="B144" t="s">
+        <v>5</v>
+      </c>
+      <c r="C144" t="s">
+        <v>23</v>
+      </c>
+      <c r="D144" s="4">
+        <v>12753941.49</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>202602</v>
+      </c>
+      <c r="B145" t="s">
+        <v>5</v>
+      </c>
+      <c r="C145" t="s">
+        <v>16</v>
+      </c>
+      <c r="D145" s="4">
+        <v>12753941.49</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>202602</v>
+      </c>
+      <c r="B146" t="s">
+        <v>5</v>
+      </c>
+      <c r="C146" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" s="4">
+        <v>13176468.49</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>202602</v>
+      </c>
+      <c r="B147" t="s">
+        <v>5</v>
+      </c>
+      <c r="C147" t="s">
+        <v>18</v>
+      </c>
+      <c r="D147" s="4">
+        <v>13400915.49</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>202602</v>
+      </c>
+      <c r="B148" t="s">
+        <v>5</v>
+      </c>
+      <c r="C148" t="s">
+        <v>19</v>
+      </c>
+      <c r="D148" s="4">
+        <v>17268085.489999998</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>202602</v>
+      </c>
+      <c r="B149" t="s">
+        <v>5</v>
+      </c>
+      <c r="C149" t="s">
+        <v>20</v>
+      </c>
+      <c r="D149" s="4">
+        <v>12529494.49</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>202602</v>
+      </c>
+      <c r="B150" t="s">
+        <v>5</v>
+      </c>
+      <c r="C150" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150" s="4">
+        <v>13825680.49</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>202602</v>
+      </c>
+      <c r="B151" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" t="s">
+        <v>24</v>
+      </c>
+      <c r="D151" s="4">
+        <v>14081026.49</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>202602</v>
+      </c>
+      <c r="B152" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" t="s">
+        <v>12</v>
+      </c>
+      <c r="D152" s="4">
+        <v>13412460.49</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>202602</v>
+      </c>
+      <c r="B153" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" t="s">
+        <v>13</v>
+      </c>
+      <c r="D153" s="4">
+        <v>13412460.49</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>202602</v>
+      </c>
+      <c r="B154" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" t="s">
+        <v>14</v>
+      </c>
+      <c r="D154" s="4">
+        <v>13412460.49</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>202602</v>
+      </c>
+      <c r="B155" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" t="s">
+        <v>15</v>
+      </c>
+      <c r="D155" s="4">
+        <v>13636907.49</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>202602</v>
+      </c>
+      <c r="B156" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" t="s">
+        <v>23</v>
+      </c>
+      <c r="D156" s="4">
+        <v>13636907.49</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <v>202602</v>
+      </c>
+      <c r="B157" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" t="s">
+        <v>16</v>
+      </c>
+      <c r="D157" s="4">
+        <v>13636907.49</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <v>202602</v>
+      </c>
+      <c r="B158" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" s="4">
+        <v>16200711.49</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <v>202602</v>
+      </c>
+      <c r="B159" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" t="s">
+        <v>18</v>
+      </c>
+      <c r="D159" s="4">
+        <v>16425158.49</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <v>202602</v>
+      </c>
+      <c r="B160" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" t="s">
+        <v>19</v>
+      </c>
+      <c r="D160" s="4">
+        <v>21909359.489999998</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A161">
+        <v>202602</v>
+      </c>
+      <c r="B161" t="s">
+        <v>6</v>
+      </c>
+      <c r="C161" t="s">
+        <v>20</v>
+      </c>
+      <c r="D161" s="4">
+        <v>13216159.49</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A162">
+        <v>202602</v>
+      </c>
+      <c r="B162" t="s">
+        <v>6</v>
+      </c>
+      <c r="C162" t="s">
+        <v>21</v>
+      </c>
+      <c r="D162" s="4">
+        <v>15948294.49</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A163">
+        <v>202602</v>
+      </c>
+      <c r="B163" t="s">
+        <v>6</v>
+      </c>
+      <c r="C163" t="s">
+        <v>24</v>
+      </c>
+      <c r="D163" s="4">
+        <v>14098662.49</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A164">
+        <v>202602</v>
+      </c>
+      <c r="B164" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" t="s">
+        <v>12</v>
+      </c>
+      <c r="D164" s="4">
+        <v>13609044.49</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A165">
+        <v>202602</v>
+      </c>
+      <c r="B165" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" t="s">
+        <v>13</v>
+      </c>
+      <c r="D165" s="4">
+        <v>13609044.49</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A166">
+        <v>202602</v>
+      </c>
+      <c r="B166" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" t="s">
+        <v>14</v>
+      </c>
+      <c r="D166" s="4">
+        <v>13609044.49</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A167">
+        <v>202602</v>
+      </c>
+      <c r="B167" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" t="s">
+        <v>15</v>
+      </c>
+      <c r="D167" s="4">
+        <v>13833491.49</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A168">
+        <v>202602</v>
+      </c>
+      <c r="B168" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" t="s">
+        <v>23</v>
+      </c>
+      <c r="D168" s="4">
+        <v>13833491.49</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A169">
+        <v>202602</v>
+      </c>
+      <c r="B169" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" t="s">
+        <v>16</v>
+      </c>
+      <c r="D169" s="4">
+        <v>13833491.49</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A170">
+        <v>202602</v>
+      </c>
+      <c r="B170" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" t="s">
+        <v>17</v>
+      </c>
+      <c r="D170" s="4">
+        <v>16416573.49</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A171">
+        <v>202602</v>
+      </c>
+      <c r="B171" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" t="s">
+        <v>18</v>
+      </c>
+      <c r="D171" s="4">
+        <v>16641020.49</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A172">
+        <v>202602</v>
+      </c>
+      <c r="B172" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" t="s">
+        <v>19</v>
+      </c>
+      <c r="D172" s="4">
+        <v>22075282.489999998</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A173">
+        <v>202602</v>
+      </c>
+      <c r="B173" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" t="s">
+        <v>20</v>
+      </c>
+      <c r="D173" s="4">
+        <v>13391356.49</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A174">
+        <v>202602</v>
+      </c>
+      <c r="B174" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" t="s">
+        <v>21</v>
+      </c>
+      <c r="D174" s="4">
+        <v>15882058.49</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A175">
+        <v>202602</v>
+      </c>
+      <c r="B175" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" t="s">
+        <v>24</v>
+      </c>
+      <c r="D175" s="4">
+        <v>14175229.49</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A176">
+        <v>202602</v>
+      </c>
+      <c r="B176" t="s">
+        <v>8</v>
+      </c>
+      <c r="C176" t="s">
+        <v>12</v>
+      </c>
+      <c r="D176" s="4">
+        <v>17946127.489999998</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A177">
+        <v>202602</v>
+      </c>
+      <c r="B177" t="s">
+        <v>8</v>
+      </c>
+      <c r="C177" t="s">
+        <v>13</v>
+      </c>
+      <c r="D177" s="4">
+        <v>17946127.489999998</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A178">
+        <v>202602</v>
+      </c>
+      <c r="B178" t="s">
+        <v>8</v>
+      </c>
+      <c r="C178" t="s">
+        <v>14</v>
+      </c>
+      <c r="D178" s="4">
+        <v>17946127.489999998</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A179">
+        <v>202602</v>
+      </c>
+      <c r="B179" t="s">
+        <v>8</v>
+      </c>
+      <c r="C179" t="s">
+        <v>15</v>
+      </c>
+      <c r="D179" s="4">
+        <v>18170574.489999998</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A180">
+        <v>202602</v>
+      </c>
+      <c r="B180" t="s">
+        <v>8</v>
+      </c>
+      <c r="C180" t="s">
+        <v>23</v>
+      </c>
+      <c r="D180" s="4">
+        <v>18170574.489999998</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A181">
+        <v>202602</v>
+      </c>
+      <c r="B181" t="s">
+        <v>8</v>
+      </c>
+      <c r="C181" t="s">
+        <v>16</v>
+      </c>
+      <c r="D181" s="4">
+        <v>18170574.489999998</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A182">
+        <v>202602</v>
+      </c>
+      <c r="B182" t="s">
+        <v>8</v>
+      </c>
+      <c r="C182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" s="4">
+        <v>20849056.489999998</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A183">
+        <v>202602</v>
+      </c>
+      <c r="B183" t="s">
+        <v>8</v>
+      </c>
+      <c r="C183" t="s">
+        <v>18</v>
+      </c>
+      <c r="D183" s="4">
+        <v>21073503.489999998</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A184">
+        <v>202602</v>
+      </c>
+      <c r="B184" t="s">
+        <v>8</v>
+      </c>
+      <c r="C184" t="s">
+        <v>19</v>
+      </c>
+      <c r="D184" s="4">
+        <v>26951577.489999998</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A185">
+        <v>202602</v>
+      </c>
+      <c r="B185" t="s">
+        <v>8</v>
+      </c>
+      <c r="C185" t="s">
+        <v>20</v>
+      </c>
+      <c r="D185" s="4">
+        <v>17775102.489999998</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A186">
+        <v>202602</v>
+      </c>
+      <c r="B186" t="s">
+        <v>8</v>
+      </c>
+      <c r="C186" t="s">
+        <v>21</v>
+      </c>
+      <c r="D186" s="4">
+        <v>20563005.489999998</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A187">
+        <v>202602</v>
+      </c>
+      <c r="B187" t="s">
+        <v>8</v>
+      </c>
+      <c r="C187" t="s">
+        <v>24</v>
+      </c>
+      <c r="D187" s="4">
+        <v>18639040.489999998</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A188">
+        <v>202602</v>
+      </c>
+      <c r="B188" t="s">
+        <v>9</v>
+      </c>
+      <c r="C188" t="s">
+        <v>12</v>
+      </c>
+      <c r="D188" s="4">
+        <v>18147373.489999998</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A189">
+        <v>202602</v>
+      </c>
+      <c r="B189" t="s">
+        <v>9</v>
+      </c>
+      <c r="C189" t="s">
+        <v>13</v>
+      </c>
+      <c r="D189" s="4">
+        <v>18147373.489999998</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A190">
+        <v>202602</v>
+      </c>
+      <c r="B190" t="s">
+        <v>9</v>
+      </c>
+      <c r="C190" t="s">
+        <v>14</v>
+      </c>
+      <c r="D190" s="4">
+        <v>18147373.489999998</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A191">
+        <v>202602</v>
+      </c>
+      <c r="B191" t="s">
+        <v>9</v>
+      </c>
+      <c r="C191" t="s">
+        <v>15</v>
+      </c>
+      <c r="D191" s="4">
+        <v>18371820.489999998</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A192">
+        <v>202602</v>
+      </c>
+      <c r="B192" t="s">
+        <v>9</v>
+      </c>
+      <c r="C192" t="s">
+        <v>23</v>
+      </c>
+      <c r="D192" s="4">
+        <v>18371820.489999998</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A193">
+        <v>202602</v>
+      </c>
+      <c r="B193" t="s">
+        <v>9</v>
+      </c>
+      <c r="C193" t="s">
+        <v>16</v>
+      </c>
+      <c r="D193" s="4">
+        <v>18371820.489999998</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A194">
+        <v>202602</v>
+      </c>
+      <c r="B194" t="s">
+        <v>9</v>
+      </c>
+      <c r="C194" t="s">
+        <v>17</v>
+      </c>
+      <c r="D194" s="4">
+        <v>21108165.489999998</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A195">
+        <v>202602</v>
+      </c>
+      <c r="B195" t="s">
+        <v>9</v>
+      </c>
+      <c r="C195" t="s">
+        <v>18</v>
+      </c>
+      <c r="D195" s="4">
+        <v>21332612.489999998</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A196">
+        <v>202602</v>
+      </c>
+      <c r="B196" t="s">
+        <v>9</v>
+      </c>
+      <c r="C196" t="s">
+        <v>19</v>
+      </c>
+      <c r="D196" s="4">
+        <v>27210687.489999998</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A197">
+        <v>202602</v>
+      </c>
+      <c r="B197" t="s">
+        <v>9</v>
+      </c>
+      <c r="C197" t="s">
+        <v>20</v>
+      </c>
+      <c r="D197" s="4">
+        <v>17948621.489999998</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A198">
+        <v>202602</v>
+      </c>
+      <c r="B198" t="s">
+        <v>9</v>
+      </c>
+      <c r="C198" t="s">
+        <v>21</v>
+      </c>
+      <c r="D198" s="4">
+        <v>20447024.489999998</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A199">
+        <v>202602</v>
+      </c>
+      <c r="B199" t="s">
+        <v>9</v>
+      </c>
+      <c r="C199" t="s">
+        <v>24</v>
+      </c>
+      <c r="D199" s="4">
+        <v>18731329.489999998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
